--- a/jogos_2025-01-06.xlsx
+++ b/jogos_2025-01-06.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,55 +927,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X4" t="n">
         <v>2.5</v>
       </c>
-      <c r="T4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.85</v>
-      </c>
       <c r="Y4" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AC4" t="n">
         <v>2.1</v>
@@ -985,25 +985,25 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '41', '58']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '53', '81']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45663.45833333334</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="N5" t="n">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.25</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X5" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="n">
         <v>2.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA5" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['59']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['35']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45663.45833333334</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="M7" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="N7" t="n">
-        <v>2.69</v>
+        <v>3.03</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="Z7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36', '75']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45663.45833333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="N8" t="n">
-        <v>2.56</v>
+        <v>2.89</v>
       </c>
       <c r="O8" t="n">
         <v>3.25</v>
       </c>
       <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['11', '41', '58']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['48', '53', '81']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45663.45833333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.83</v>
-      </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['36', '75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45663.45833333334</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Urooba</t>
+          <t>Dibba Al Hisn</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="M10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>7.48</v>
       </c>
       <c r="O10" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.21</v>
+        <v>2.81</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['1', '15', '35', '41', '69', '90+2']</t>
+          <t>['6', '37', '75', '88']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AG10" t="n">
         <v>1.02</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.7</v>
+        <v>3.64</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45663.53125</v>
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dibba Al Hisn</t>
+          <t>Al Urooba</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="M11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="N11" t="n">
-        <v>7.48</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P11" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="V11" t="n">
         <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['6', '37', '75', '88']</t>
+          <t>['1', '15', '35', '41', '69', '90+2']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
         <v>1.02</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.64</v>
+        <v>4.7</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45663.53125</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['19', '71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74', '90+10']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45663.5625</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.5</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="AD14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['19', '71']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>4.75</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['74', '90+10']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45663.5625</v>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>5.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '90+7']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.73</v>
+        <v>3.4</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45663.58333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2604,22 +2604,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
         <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
@@ -2628,59 +2628,59 @@
         <v>2.75</v>
       </c>
       <c r="T17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA17" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AC17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.09</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45663.58333333334</v>
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>5.75</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.3</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI18" t="n">
         <v>2.38</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['32', '90+7']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['67']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45663.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O19" t="n">
         <v>3.2</v>
       </c>
-      <c r="N19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.75</v>
-      </c>
       <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD19" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W19" t="n">
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.38</v>
       </c>
-      <c r="X19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['28']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45663.58333333334</v>
